--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/120.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/120.xlsx
@@ -426,13 +426,13 @@
         <v>-6.561003828149344</v>
       </c>
       <c r="E2">
-        <v>-22.89332203066845</v>
+        <v>-25.99852835704607</v>
       </c>
       <c r="F2">
-        <v>-2.672200730711932</v>
+        <v>-2.152829279769893</v>
       </c>
       <c r="G2">
-        <v>-11.53012143993683</v>
+        <v>-14.1193603512933</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.802322050477975</v>
       </c>
       <c r="E3">
-        <v>-23.32877556277202</v>
+        <v>-25.62340768414668</v>
       </c>
       <c r="F3">
-        <v>-2.40802856738735</v>
+        <v>-2.466701830527639</v>
       </c>
       <c r="G3">
-        <v>-11.35181876773722</v>
+        <v>-14.10763936481151</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.07382109998643</v>
       </c>
       <c r="E4">
-        <v>-22.90204840008123</v>
+        <v>-25.51026828953905</v>
       </c>
       <c r="F4">
-        <v>-2.557665683396456</v>
+        <v>-2.235290769616375</v>
       </c>
       <c r="G4">
-        <v>-11.66419191318623</v>
+        <v>-13.69227183709024</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.337391536813744</v>
       </c>
       <c r="E5">
-        <v>-23.0222341002448</v>
+        <v>-25.80854981547628</v>
       </c>
       <c r="F5">
-        <v>-2.478128330481856</v>
+        <v>-2.302455627002761</v>
       </c>
       <c r="G5">
-        <v>-11.3526430935765</v>
+        <v>-13.77178948567076</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.579431288373726</v>
       </c>
       <c r="E6">
-        <v>-23.80059274115719</v>
+        <v>-25.45423748064215</v>
       </c>
       <c r="F6">
-        <v>-2.573634950187624</v>
+        <v>-2.250188957355724</v>
       </c>
       <c r="G6">
-        <v>-11.07998987350767</v>
+        <v>-13.60329430463124</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.766108558585726</v>
       </c>
       <c r="E7">
-        <v>-24.5310265416464</v>
+        <v>-26.67627789093005</v>
       </c>
       <c r="F7">
-        <v>-2.455464198341261</v>
+        <v>-2.361423788938447</v>
       </c>
       <c r="G7">
-        <v>-10.94122504668358</v>
+        <v>-13.49859664667902</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.878060124353161</v>
       </c>
       <c r="E8">
-        <v>-24.01795949352537</v>
+        <v>-26.69027087561375</v>
       </c>
       <c r="F8">
-        <v>-2.27626513482845</v>
+        <v>-2.060438978233455</v>
       </c>
       <c r="G8">
-        <v>-10.7718774001677</v>
+        <v>-12.92508601381953</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.894147176326887</v>
       </c>
       <c r="E9">
-        <v>-25.64362279211693</v>
+        <v>-27.49472258375833</v>
       </c>
       <c r="F9">
-        <v>-2.302585680685001</v>
+        <v>-2.090568357408079</v>
       </c>
       <c r="G9">
-        <v>-10.78166337278178</v>
+        <v>-13.206601564297</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.793107891274996</v>
       </c>
       <c r="E10">
-        <v>-25.53067359341761</v>
+        <v>-27.88627256035754</v>
       </c>
       <c r="F10">
-        <v>-2.502112051895109</v>
+        <v>-2.221206867033978</v>
       </c>
       <c r="G10">
-        <v>-10.39024764203713</v>
+        <v>-12.639223717049</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.571736215904514</v>
       </c>
       <c r="E11">
-        <v>-26.25831332544409</v>
+        <v>-29.08344259139531</v>
       </c>
       <c r="F11">
-        <v>-2.356461039828275</v>
+        <v>-2.028456541178769</v>
       </c>
       <c r="G11">
-        <v>-9.990813769996368</v>
+        <v>-12.42323379443033</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.234311525012397</v>
       </c>
       <c r="E12">
-        <v>-26.77615338516921</v>
+        <v>-29.19237503364982</v>
       </c>
       <c r="F12">
-        <v>-2.378016816383924</v>
+        <v>-2.089557749176663</v>
       </c>
       <c r="G12">
-        <v>-10.38860230090411</v>
+        <v>-12.31460155310469</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.790343743201644</v>
       </c>
       <c r="E13">
-        <v>-27.24077481835619</v>
+        <v>-29.67506507812741</v>
       </c>
       <c r="F13">
-        <v>-2.460173467026176</v>
+        <v>-2.111364521055361</v>
       </c>
       <c r="G13">
-        <v>-9.879509918420531</v>
+        <v>-11.78202747111105</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.273083882553179</v>
       </c>
       <c r="E14">
-        <v>-28.23504204300629</v>
+        <v>-29.35104823440459</v>
       </c>
       <c r="F14">
-        <v>-2.142382738453188</v>
+        <v>-2.358377053630951</v>
       </c>
       <c r="G14">
-        <v>-8.981570788530771</v>
+        <v>-11.59620323944622</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.71412259437237</v>
       </c>
       <c r="E15">
-        <v>-28.98724421805037</v>
+        <v>-31.01587377621448</v>
       </c>
       <c r="F15">
-        <v>-1.744629704487963</v>
+        <v>-1.786809344271111</v>
       </c>
       <c r="G15">
-        <v>-8.791757349491119</v>
+        <v>-10.24621573726006</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.142520851993866</v>
       </c>
       <c r="E16">
-        <v>-29.8697079479251</v>
+        <v>-30.82917837830025</v>
       </c>
       <c r="F16">
-        <v>-1.906474470912125</v>
+        <v>-1.892781557743849</v>
       </c>
       <c r="G16">
-        <v>-8.516270302440667</v>
+        <v>-10.13209130088477</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.594885556188833</v>
       </c>
       <c r="E17">
-        <v>-29.96797583389154</v>
+        <v>-32.34824366298825</v>
       </c>
       <c r="F17">
-        <v>-1.501174181539994</v>
+        <v>-1.914884885152748</v>
       </c>
       <c r="G17">
-        <v>-7.75840035431747</v>
+        <v>-9.765236507495969</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.092897184210586</v>
       </c>
       <c r="E18">
-        <v>-30.97350084492471</v>
+        <v>-32.66658632877947</v>
       </c>
       <c r="F18">
-        <v>-1.595659424238111</v>
+        <v>-1.940782135266469</v>
       </c>
       <c r="G18">
-        <v>-7.86033536201717</v>
+        <v>-9.57140406617164</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.649653959770293</v>
       </c>
       <c r="E19">
-        <v>-31.59923859059359</v>
+        <v>-33.53541482341709</v>
       </c>
       <c r="F19">
-        <v>-1.423859338367105</v>
+        <v>-1.621633712520293</v>
       </c>
       <c r="G19">
-        <v>-7.031490628077539</v>
+        <v>-8.855859442768027</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.279435457198685</v>
       </c>
       <c r="E20">
-        <v>-32.42688740684246</v>
+        <v>-34.31219981961181</v>
       </c>
       <c r="F20">
-        <v>-1.188558264132294</v>
+        <v>-1.328884530533933</v>
       </c>
       <c r="G20">
-        <v>-6.948111228125455</v>
+        <v>-9.254687484975104</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.979942072567856</v>
       </c>
       <c r="E21">
-        <v>-33.31238974277633</v>
+        <v>-34.75937983515825</v>
       </c>
       <c r="F21">
-        <v>-1.315088071440308</v>
+        <v>-1.562825425493347</v>
       </c>
       <c r="G21">
-        <v>-7.113267723988616</v>
+        <v>-8.742900318422555</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.744936645977396</v>
       </c>
       <c r="E22">
-        <v>-34.16135635041632</v>
+        <v>-35.36352808099556</v>
       </c>
       <c r="F22">
-        <v>-1.054979050226457</v>
+        <v>-1.278248087935605</v>
       </c>
       <c r="G22">
-        <v>-7.011246642104896</v>
+        <v>-8.86238121748039</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.569708498188398</v>
       </c>
       <c r="E23">
-        <v>-33.63021842676767</v>
+        <v>-35.86466712858039</v>
       </c>
       <c r="F23">
-        <v>-0.8551113916463954</v>
+        <v>-1.089034062522948</v>
       </c>
       <c r="G23">
-        <v>-6.672442101070343</v>
+        <v>-8.785652703516702</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.43932350336808</v>
       </c>
       <c r="E24">
-        <v>-34.58024246036283</v>
+        <v>-36.12824016548583</v>
       </c>
       <c r="F24">
-        <v>-1.018996426983652</v>
+        <v>-0.8357300795230954</v>
       </c>
       <c r="G24">
-        <v>-6.744492814187041</v>
+        <v>-8.958886930495686</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.34225686314507</v>
       </c>
       <c r="E25">
-        <v>-35.06672510182184</v>
+        <v>-36.31274378198035</v>
       </c>
       <c r="F25">
-        <v>-0.7001677540549562</v>
+        <v>-0.7847747154746894</v>
       </c>
       <c r="G25">
-        <v>-6.384636514068263</v>
+        <v>-9.154619624959555</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.271162418811572</v>
       </c>
       <c r="E26">
-        <v>-35.21367861184475</v>
+        <v>-37.0303303017098</v>
       </c>
       <c r="F26">
-        <v>-0.7677244292228672</v>
+        <v>-0.7342749534978231</v>
       </c>
       <c r="G26">
-        <v>-6.493914311774066</v>
+        <v>-8.698916410387797</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.214910099412535</v>
       </c>
       <c r="E27">
-        <v>-35.27135099256943</v>
+        <v>-36.54470580607525</v>
       </c>
       <c r="F27">
-        <v>-0.4878190838169142</v>
+        <v>-0.9636474022307978</v>
       </c>
       <c r="G27">
-        <v>-6.407780537933308</v>
+        <v>-8.845523919594422</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.16974765569715</v>
       </c>
       <c r="E28">
-        <v>-34.343007028286</v>
+        <v>-36.60263630981837</v>
       </c>
       <c r="F28">
-        <v>-0.8140442492852071</v>
+        <v>-0.6712916947607683</v>
       </c>
       <c r="G28">
-        <v>-6.243004754807163</v>
+        <v>-9.218506532776409</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.136167744432196</v>
       </c>
       <c r="E29">
-        <v>-35.04990861359435</v>
+        <v>-37.07334174783465</v>
       </c>
       <c r="F29">
-        <v>-0.3405312177621481</v>
+        <v>-0.8481116870927395</v>
       </c>
       <c r="G29">
-        <v>-6.737696264194918</v>
+        <v>-8.883926247849967</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.112066822211601</v>
       </c>
       <c r="E30">
-        <v>-35.0831747836547</v>
+        <v>-36.74886752823706</v>
       </c>
       <c r="F30">
-        <v>-0.3668633607623388</v>
+        <v>-0.7889472020825905</v>
       </c>
       <c r="G30">
-        <v>-6.504355772404927</v>
+        <v>-8.984166256233561</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.101307494889538</v>
       </c>
       <c r="E31">
-        <v>-34.10075178277167</v>
+        <v>-36.58338350257476</v>
       </c>
       <c r="F31">
-        <v>-0.5973168289559668</v>
+        <v>-0.7363698946595031</v>
       </c>
       <c r="G31">
-        <v>-6.985437629080738</v>
+        <v>-9.361234082611009</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.1100725431107</v>
       </c>
       <c r="E32">
-        <v>-34.3274788909137</v>
+        <v>-36.08758579008197</v>
       </c>
       <c r="F32">
-        <v>-0.5184695060878988</v>
+        <v>-0.8045751815038059</v>
       </c>
       <c r="G32">
-        <v>-6.900244050173133</v>
+        <v>-9.658656804404671</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.139716335097495</v>
       </c>
       <c r="E33">
-        <v>-34.14372700110446</v>
+        <v>-35.58487536201648</v>
       </c>
       <c r="F33">
-        <v>-0.5830921039150938</v>
+        <v>-0.8038197104324528</v>
       </c>
       <c r="G33">
-        <v>-7.313760982937958</v>
+        <v>-9.253919438409994</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.194863540652972</v>
       </c>
       <c r="E34">
-        <v>-33.80909315007065</v>
+        <v>-35.28076342579438</v>
       </c>
       <c r="F34">
-        <v>-0.4863884933122795</v>
+        <v>-0.6968575979133694</v>
       </c>
       <c r="G34">
-        <v>-8.203817703898713</v>
+        <v>-9.978107896216645</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.279481098750341</v>
       </c>
       <c r="E35">
-        <v>-32.64016947565572</v>
+        <v>-35.31600627475907</v>
       </c>
       <c r="F35">
-        <v>-0.6347300427034065</v>
+        <v>-0.6678614253457755</v>
       </c>
       <c r="G35">
-        <v>-7.976843391180741</v>
+        <v>-10.03430771729131</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.391229184065342</v>
       </c>
       <c r="E36">
-        <v>-33.15625248746586</v>
+        <v>-34.38069751745184</v>
       </c>
       <c r="F36">
-        <v>-0.5926332396605385</v>
+        <v>-0.7282295281921923</v>
       </c>
       <c r="G36">
-        <v>-7.734779611894771</v>
+        <v>-9.998540583285026</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.532864794607408</v>
       </c>
       <c r="E37">
-        <v>-31.68809404333509</v>
+        <v>-34.8705176442545</v>
       </c>
       <c r="F37">
-        <v>-0.2163075853035286</v>
+        <v>-0.5649508577937846</v>
       </c>
       <c r="G37">
-        <v>-8.068436254615756</v>
+        <v>-10.04090894509662</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.705859402748877</v>
       </c>
       <c r="E38">
-        <v>-32.13060973065362</v>
+        <v>-33.48918589650979</v>
       </c>
       <c r="F38">
-        <v>-0.4359243511337336</v>
+        <v>-0.7524319385997855</v>
       </c>
       <c r="G38">
-        <v>-8.138517193136588</v>
+        <v>-9.860921205217522</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.904039342519722</v>
       </c>
       <c r="E39">
-        <v>-31.28894755158801</v>
+        <v>-32.8338070242237</v>
       </c>
       <c r="F39">
-        <v>-0.2397702636204219</v>
+        <v>-0.4978945165371646</v>
       </c>
       <c r="G39">
-        <v>-8.17298659329148</v>
+        <v>-10.08519080222991</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.128024760772118</v>
       </c>
       <c r="E40">
-        <v>-31.02454580393917</v>
+        <v>-32.28669943698701</v>
       </c>
       <c r="F40">
-        <v>-0.3097954736486753</v>
+        <v>-0.04326826179793433</v>
       </c>
       <c r="G40">
-        <v>-8.296549394999237</v>
+        <v>-9.955337963997538</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.375535949888928</v>
       </c>
       <c r="E41">
-        <v>-30.13390591424359</v>
+        <v>-32.18676960105975</v>
       </c>
       <c r="F41">
-        <v>-0.1664821143925412</v>
+        <v>-0.4353892257915251</v>
       </c>
       <c r="G41">
-        <v>-8.354762027761783</v>
+        <v>-9.638290328247075</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.636500929936287</v>
       </c>
       <c r="E42">
-        <v>-29.22212710788022</v>
+        <v>-31.98528194279947</v>
       </c>
       <c r="F42">
-        <v>-0.01517997990380869</v>
+        <v>-0.316936000660807</v>
       </c>
       <c r="G42">
-        <v>-8.207661247269806</v>
+        <v>-10.07657345219119</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.912089969834811</v>
       </c>
       <c r="E43">
-        <v>-28.65464138760901</v>
+        <v>-30.57212860820286</v>
       </c>
       <c r="F43">
-        <v>0.1586164714079444</v>
+        <v>-0.06380763155034808</v>
       </c>
       <c r="G43">
-        <v>-7.981766172397637</v>
+        <v>-10.74737605263155</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.200645401743112</v>
       </c>
       <c r="E44">
-        <v>-28.62825849804032</v>
+        <v>-30.50748917021737</v>
       </c>
       <c r="F44">
-        <v>0.01459154455280554</v>
+        <v>0.02208909791554386</v>
       </c>
       <c r="G44">
-        <v>-8.530489095531836</v>
+        <v>-10.5370438523395</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.493981514046335</v>
       </c>
       <c r="E45">
-        <v>-27.58567698420239</v>
+        <v>-30.03133824220687</v>
       </c>
       <c r="F45">
-        <v>-0.009089822758426727</v>
+        <v>0.08523637339835298</v>
       </c>
       <c r="G45">
-        <v>-8.151484600013914</v>
+        <v>-10.18423570367383</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.797446710715282</v>
       </c>
       <c r="E46">
-        <v>-27.49250363149457</v>
+        <v>-29.46095882704475</v>
       </c>
       <c r="F46">
-        <v>0.2518475658582232</v>
+        <v>0.07728404633147773</v>
       </c>
       <c r="G46">
-        <v>-9.089759416754154</v>
+        <v>-10.72011371011565</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.110911704590001</v>
       </c>
       <c r="E47">
-        <v>-26.47979193221123</v>
+        <v>-28.49817355369598</v>
       </c>
       <c r="F47">
-        <v>0.2880157433992552</v>
+        <v>-0.2851614838242236</v>
       </c>
       <c r="G47">
-        <v>-8.390757589410278</v>
+        <v>-10.66068941768573</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.429978728780752</v>
       </c>
       <c r="E48">
-        <v>-25.9194385585021</v>
+        <v>-27.40240964111197</v>
       </c>
       <c r="F48">
-        <v>0.4443013361832295</v>
+        <v>0.133167368059138</v>
       </c>
       <c r="G48">
-        <v>-8.465367354228833</v>
+        <v>-10.91502869983132</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.764639274079591</v>
       </c>
       <c r="E49">
-        <v>-25.33816816335155</v>
+        <v>-27.54712155650109</v>
       </c>
       <c r="F49">
-        <v>0.3801318553253658</v>
+        <v>-0.1292710222913846</v>
       </c>
       <c r="G49">
-        <v>-8.505067416335773</v>
+        <v>-9.750610517303468</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.116750920589306</v>
       </c>
       <c r="E50">
-        <v>-24.36061100778975</v>
+        <v>-27.15869622696717</v>
       </c>
       <c r="F50">
-        <v>0.5113394533569878</v>
+        <v>0.1221517383367101</v>
       </c>
       <c r="G50">
-        <v>-8.485300148920786</v>
+        <v>-10.5639188610273</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.483769088441545</v>
       </c>
       <c r="E51">
-        <v>-24.25245746306456</v>
+        <v>-26.01250775630774</v>
       </c>
       <c r="F51">
-        <v>0.537921763312824</v>
+        <v>-0.1129886326219575</v>
       </c>
       <c r="G51">
-        <v>-8.412196682322598</v>
+        <v>-10.7408807622835</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.873471275962684</v>
       </c>
       <c r="E52">
-        <v>-23.50438978478948</v>
+        <v>-26.69088221960478</v>
       </c>
       <c r="F52">
-        <v>0.2136697689979995</v>
+        <v>-0.03314312703351597</v>
       </c>
       <c r="G52">
-        <v>-8.356370952893869</v>
+        <v>-10.89878054232458</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.281144693479983</v>
       </c>
       <c r="E53">
-        <v>-22.60665151208688</v>
+        <v>-25.69913282650295</v>
       </c>
       <c r="F53">
-        <v>0.5266932431678767</v>
+        <v>0.08751521212345442</v>
       </c>
       <c r="G53">
-        <v>-8.521782360763552</v>
+        <v>-10.6222374312471</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.700151583787433</v>
       </c>
       <c r="E54">
-        <v>-22.576020913899</v>
+        <v>-25.31225170660565</v>
       </c>
       <c r="F54">
-        <v>0.7069609006302995</v>
+        <v>0.2640253950467787</v>
       </c>
       <c r="G54">
-        <v>-8.731651084680111</v>
+        <v>-10.93629895492114</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.131594035525726</v>
       </c>
       <c r="E55">
-        <v>-22.45725262609983</v>
+        <v>-23.84325096630944</v>
       </c>
       <c r="F55">
-        <v>0.493701026249178</v>
+        <v>0.2780778196678695</v>
       </c>
       <c r="G55">
-        <v>-8.539417636851251</v>
+        <v>-11.2147621824114</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.562177507732198</v>
       </c>
       <c r="E56">
-        <v>-21.35170720965925</v>
+        <v>-24.91357844039237</v>
       </c>
       <c r="F56">
-        <v>0.3436381293950336</v>
+        <v>0.2588472704118789</v>
       </c>
       <c r="G56">
-        <v>-8.938854819437555</v>
+        <v>-10.92210333564875</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.982777321179332</v>
       </c>
       <c r="E57">
-        <v>-21.07376306049047</v>
+        <v>-24.00787458191029</v>
       </c>
       <c r="F57">
-        <v>0.6213333905703174</v>
+        <v>0.04499925517476979</v>
       </c>
       <c r="G57">
-        <v>-8.906073797507691</v>
+        <v>-11.29914798820742</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.389646727604488</v>
       </c>
       <c r="E58">
-        <v>-20.37167750728927</v>
+        <v>-23.46204855281776</v>
       </c>
       <c r="F58">
-        <v>0.740325882880258</v>
+        <v>0.02467029074266712</v>
       </c>
       <c r="G58">
-        <v>-8.920491223331219</v>
+        <v>-11.02921603657186</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.765098591855065</v>
       </c>
       <c r="E59">
-        <v>-20.31493572797316</v>
+        <v>-22.66213890410287</v>
       </c>
       <c r="F59">
-        <v>0.2838242043410897</v>
+        <v>-0.01355637979432166</v>
       </c>
       <c r="G59">
-        <v>-9.066724640891906</v>
+        <v>-10.70632859849013</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.10298645573033</v>
       </c>
       <c r="E60">
-        <v>-20.2491868138558</v>
+        <v>-22.80906524328174</v>
       </c>
       <c r="F60">
-        <v>0.4894440461661914</v>
+        <v>0.06636699232998304</v>
       </c>
       <c r="G60">
-        <v>-9.264668779776008</v>
+        <v>-11.21643731845427</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.40001324283047</v>
       </c>
       <c r="E61">
-        <v>-19.8303074966203</v>
+        <v>-23.15616824749566</v>
       </c>
       <c r="F61">
-        <v>0.1884302426021014</v>
+        <v>0.1161369626249829</v>
       </c>
       <c r="G61">
-        <v>-8.677877893485729</v>
+        <v>-11.60766103755764</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.64038036101434</v>
       </c>
       <c r="E62">
-        <v>-18.27593596433149</v>
+        <v>-22.61719832805075</v>
       </c>
       <c r="F62">
-        <v>0.3401010005850797</v>
+        <v>-0.177501885951983</v>
       </c>
       <c r="G62">
-        <v>-9.212001310791742</v>
+        <v>-11.41516605663118</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.82690198125883</v>
       </c>
       <c r="E63">
-        <v>-19.51353621130975</v>
+        <v>-22.03046206477293</v>
       </c>
       <c r="F63">
-        <v>0.2095411858624468</v>
+        <v>0.006058531936567832</v>
       </c>
       <c r="G63">
-        <v>-9.323139635090616</v>
+        <v>-11.51708120105764</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.95982076265095</v>
       </c>
       <c r="E64">
-        <v>-19.15359498328408</v>
+        <v>-22.43021310780003</v>
       </c>
       <c r="F64">
-        <v>0.0253868285460887</v>
+        <v>-0.08107163659209257</v>
       </c>
       <c r="G64">
-        <v>-9.150832360862628</v>
+        <v>-11.22377679791483</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.02694822512546</v>
       </c>
       <c r="E65">
-        <v>-18.58427070256575</v>
+        <v>-22.47719602562961</v>
       </c>
       <c r="F65">
-        <v>-0.344762518455648</v>
+        <v>-0.08897757508441105</v>
       </c>
       <c r="G65">
-        <v>-9.299124937748742</v>
+        <v>-10.68228079569286</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.03621727984158</v>
       </c>
       <c r="E66">
-        <v>-18.1043158563888</v>
+        <v>-22.12949526284667</v>
       </c>
       <c r="F66">
-        <v>-0.1863173718525754</v>
+        <v>-0.5721477137893067</v>
       </c>
       <c r="G66">
-        <v>-9.368831784623636</v>
+        <v>-11.73409077170241</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.98649113344907</v>
       </c>
       <c r="E67">
-        <v>-18.88189559977187</v>
+        <v>-21.79872193590441</v>
       </c>
       <c r="F67">
-        <v>-0.3969132166662936</v>
+        <v>-0.5588068567672206</v>
       </c>
       <c r="G67">
-        <v>-9.156983354474594</v>
+        <v>-11.88390288899105</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.8685263976096</v>
       </c>
       <c r="E68">
-        <v>-18.05226104767063</v>
+        <v>-22.07976808976845</v>
       </c>
       <c r="F68">
-        <v>-0.357921963016521</v>
+        <v>-0.800864923906667</v>
       </c>
       <c r="G68">
-        <v>-9.473729730580983</v>
+        <v>-10.73708356654996</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.69560193071799</v>
       </c>
       <c r="E69">
-        <v>-18.34546615424526</v>
+        <v>-21.66167219853627</v>
       </c>
       <c r="F69">
-        <v>-0.6500755488402674</v>
+        <v>-0.4446619704984628</v>
       </c>
       <c r="G69">
-        <v>-8.85116839973888</v>
+        <v>-11.21260370671979</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.46961515827136</v>
       </c>
       <c r="E70">
-        <v>-18.89264166859207</v>
+        <v>-21.3112317089787</v>
       </c>
       <c r="F70">
-        <v>-0.8605529371153854</v>
+        <v>-1.005791422215625</v>
       </c>
       <c r="G70">
-        <v>-9.008296822669308</v>
+        <v>-10.8405314935611</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.19004116168974</v>
       </c>
       <c r="E71">
-        <v>-18.16655973162423</v>
+        <v>-20.9405308267108</v>
       </c>
       <c r="F71">
-        <v>-0.7030090542465586</v>
+        <v>-1.08555491943119</v>
       </c>
       <c r="G71">
-        <v>-8.20869082693252</v>
+        <v>-10.75567227975296</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.874692559262309</v>
       </c>
       <c r="E72">
-        <v>-18.47078261545953</v>
+        <v>-21.6923299675682</v>
       </c>
       <c r="F72">
-        <v>-1.168991397710767</v>
+        <v>-0.6877066232146433</v>
       </c>
       <c r="G72">
-        <v>-8.904941590933261</v>
+        <v>-10.42450516727751</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.528859100060043</v>
       </c>
       <c r="E73">
-        <v>-18.09228370095042</v>
+        <v>-21.16983463656319</v>
       </c>
       <c r="F73">
-        <v>-1.104937888289296</v>
+        <v>-1.127395756946593</v>
       </c>
       <c r="G73">
-        <v>-8.803827598527301</v>
+        <v>-11.12442401573576</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.16028856756974</v>
       </c>
       <c r="E74">
-        <v>-17.92201307826202</v>
+        <v>-21.76080049456418</v>
       </c>
       <c r="F74">
-        <v>-1.38243516965531</v>
+        <v>-1.228591603974789</v>
       </c>
       <c r="G74">
-        <v>-8.364657248378665</v>
+        <v>-10.38649679394114</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.789891848461224</v>
       </c>
       <c r="E75">
-        <v>-18.28878324509125</v>
+        <v>-21.4653266225117</v>
       </c>
       <c r="F75">
-        <v>-1.249763846422941</v>
+        <v>-1.273991936220021</v>
       </c>
       <c r="G75">
-        <v>-8.127337480850469</v>
+        <v>-9.980398793729821</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.424716438763859</v>
       </c>
       <c r="E76">
-        <v>-18.87528402772067</v>
+        <v>-21.90192585853922</v>
       </c>
       <c r="F76">
-        <v>-1.456154069932647</v>
+        <v>-1.431005663951056</v>
       </c>
       <c r="G76">
-        <v>-7.774072476900381</v>
+        <v>-9.872388934965558</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.077512065172094</v>
       </c>
       <c r="E77">
-        <v>-19.05817097899445</v>
+        <v>-21.41730668413437</v>
       </c>
       <c r="F77">
-        <v>-1.600429992110834</v>
+        <v>-1.705799982481736</v>
       </c>
       <c r="G77">
-        <v>-7.785427648100081</v>
+        <v>-10.47643769515206</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.768888009566791</v>
       </c>
       <c r="E78">
-        <v>-18.2605346242314</v>
+        <v>-21.87198811687451</v>
       </c>
       <c r="F78">
-        <v>-1.788476019485544</v>
+        <v>-1.468667387919336</v>
       </c>
       <c r="G78">
-        <v>-7.704964838768094</v>
+        <v>-9.55754943308979</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.503437005874339</v>
       </c>
       <c r="E79">
-        <v>-18.96234394051814</v>
+        <v>-22.65217626128599</v>
       </c>
       <c r="F79">
-        <v>-1.624402116380449</v>
+        <v>-1.71568406233194</v>
       </c>
       <c r="G79">
-        <v>-7.570801670243591</v>
+        <v>-10.13619637735346</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.292866571197732</v>
       </c>
       <c r="E80">
-        <v>-20.45384213968444</v>
+        <v>-22.95602328177865</v>
       </c>
       <c r="F80">
-        <v>-1.692185764216727</v>
+        <v>-1.503798449472063</v>
       </c>
       <c r="G80">
-        <v>-7.254045362500584</v>
+        <v>-9.582550673002366</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.14953735965389</v>
       </c>
       <c r="E81">
-        <v>-20.42940196546505</v>
+        <v>-23.33040128494078</v>
       </c>
       <c r="F81">
-        <v>-1.914787137799218</v>
+        <v>-1.776068732526413</v>
       </c>
       <c r="G81">
-        <v>-7.020893571806332</v>
+        <v>-9.656362596345957</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.067834155974385</v>
       </c>
       <c r="E82">
-        <v>-20.30629087109252</v>
+        <v>-22.69072263203929</v>
       </c>
       <c r="F82">
-        <v>-1.66842321690002</v>
+        <v>-2.005714542502311</v>
       </c>
       <c r="G82">
-        <v>-7.586675736104396</v>
+        <v>-9.797388525773369</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.052526881083711</v>
       </c>
       <c r="E83">
-        <v>-20.97441286923619</v>
+        <v>-23.86534086251886</v>
       </c>
       <c r="F83">
-        <v>-2.016104754835626</v>
+        <v>-1.721718718861335</v>
       </c>
       <c r="G83">
-        <v>-6.991409853233583</v>
+        <v>-9.624945519178272</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.106642843425376</v>
       </c>
       <c r="E84">
-        <v>-21.81568559953714</v>
+        <v>-24.65669622383326</v>
       </c>
       <c r="F84">
-        <v>-2.472116039872337</v>
+        <v>-1.874932725315728</v>
       </c>
       <c r="G84">
-        <v>-6.993644471472591</v>
+        <v>-9.196925086405901</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.216725451958016</v>
       </c>
       <c r="E85">
-        <v>-22.6211245150154</v>
+        <v>-24.90788162009072</v>
       </c>
       <c r="F85">
-        <v>-1.960211492699132</v>
+        <v>-1.847122774868943</v>
       </c>
       <c r="G85">
-        <v>-6.897330770098574</v>
+        <v>-9.146545204389271</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.383566768550921</v>
       </c>
       <c r="E86">
-        <v>-23.23808834229442</v>
+        <v>-26.59913986468339</v>
       </c>
       <c r="F86">
-        <v>-2.156359781640624</v>
+        <v>-2.103994536272653</v>
       </c>
       <c r="G86">
-        <v>-6.866847266772965</v>
+        <v>-9.505292471752394</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.603625804184542</v>
       </c>
       <c r="E87">
-        <v>-24.77747062561783</v>
+        <v>-27.06557268747343</v>
       </c>
       <c r="F87">
-        <v>-2.163337120274404</v>
+        <v>-2.152265989935989</v>
       </c>
       <c r="G87">
-        <v>-6.732253727328356</v>
+        <v>-8.894947053950201</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.85756717944603</v>
       </c>
       <c r="E88">
-        <v>-25.66765087520163</v>
+        <v>-28.13522089045521</v>
       </c>
       <c r="F88">
-        <v>-2.342826940745598</v>
+        <v>-2.041753494728507</v>
       </c>
       <c r="G88">
-        <v>-6.701780155639365</v>
+        <v>-9.072223457032635</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.146084900071967</v>
       </c>
       <c r="E89">
-        <v>-26.61966290888615</v>
+        <v>-29.0675521761024</v>
       </c>
       <c r="F89">
-        <v>-2.335885221910138</v>
+        <v>-2.166245518225633</v>
       </c>
       <c r="G89">
-        <v>-6.080225230641199</v>
+        <v>-9.393134499427426</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.463542289768148</v>
       </c>
       <c r="E90">
-        <v>-27.72658498142506</v>
+        <v>-29.95043931829684</v>
       </c>
       <c r="F90">
-        <v>-2.155853649157514</v>
+        <v>-2.517204077606714</v>
       </c>
       <c r="G90">
-        <v>-6.72020003101987</v>
+        <v>-9.771258389831903</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.791427892933138</v>
       </c>
       <c r="E91">
-        <v>-29.50586996801583</v>
+        <v>-31.57079977382542</v>
       </c>
       <c r="F91">
-        <v>-2.445538700120917</v>
+        <v>-2.22653078433177</v>
       </c>
       <c r="G91">
-        <v>-6.524113108183298</v>
+        <v>-9.299926089769246</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.133760616862926</v>
       </c>
       <c r="E92">
-        <v>-30.77590541007402</v>
+        <v>-33.3133135514739</v>
       </c>
       <c r="F92">
-        <v>-2.484824024198684</v>
+        <v>-2.794934130212915</v>
       </c>
       <c r="G92">
-        <v>-6.729721159990813</v>
+        <v>-9.607005672900963</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.484912567986962</v>
       </c>
       <c r="E93">
-        <v>-31.79368673600894</v>
+        <v>-33.96418885635935</v>
       </c>
       <c r="F93">
-        <v>-2.588998680407347</v>
+        <v>-2.6777541057803</v>
       </c>
       <c r="G93">
-        <v>-7.518650646363452</v>
+        <v>-9.984735608386266</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.825916746516572</v>
       </c>
       <c r="E94">
-        <v>-33.1297065728329</v>
+        <v>-35.32858863978938</v>
       </c>
       <c r="F94">
-        <v>-2.600281044433476</v>
+        <v>-2.643120064669253</v>
       </c>
       <c r="G94">
-        <v>-7.645795458344701</v>
+        <v>-9.598818693782345</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.15935041303618</v>
       </c>
       <c r="E95">
-        <v>-35.31667875314921</v>
+        <v>-36.68952866907755</v>
       </c>
       <c r="F95">
-        <v>-2.79421345057248</v>
+        <v>-2.678051489677905</v>
       </c>
       <c r="G95">
-        <v>-7.527171990581536</v>
+        <v>-9.792995431842757</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.46896859590523</v>
       </c>
       <c r="E96">
-        <v>-36.85207597934588</v>
+        <v>-39.56416774135463</v>
       </c>
       <c r="F96">
-        <v>-2.912407396706122</v>
+        <v>-2.970070879982398</v>
       </c>
       <c r="G96">
-        <v>-7.498648330215175</v>
+        <v>-9.51108261590058</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.73491483175148</v>
       </c>
       <c r="E97">
-        <v>-38.55450596931546</v>
+        <v>-40.78630098535969</v>
       </c>
       <c r="F97">
-        <v>-3.033093900354787</v>
+        <v>-3.010301371266759</v>
       </c>
       <c r="G97">
-        <v>-8.196220001886086</v>
+        <v>-10.23047409322083</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.94628013444256</v>
       </c>
       <c r="E98">
-        <v>-39.88756871261241</v>
+        <v>-42.11153173286037</v>
       </c>
       <c r="F98">
-        <v>-3.098240854747954</v>
+        <v>-3.079902457184779</v>
       </c>
       <c r="G98">
-        <v>-8.300575018374992</v>
+        <v>-10.37258588158512</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.09400526731292</v>
       </c>
       <c r="E99">
-        <v>-42.71848536834543</v>
+        <v>-43.70807694358261</v>
       </c>
       <c r="F99">
-        <v>-3.118728865721395</v>
+        <v>-3.342079911803419</v>
       </c>
       <c r="G99">
-        <v>-8.288676917706852</v>
+        <v>-10.81241834084161</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.1437975548588</v>
       </c>
       <c r="E100">
-        <v>-44.06869291423543</v>
+        <v>-46.22663304768856</v>
       </c>
       <c r="F100">
-        <v>-3.446222261683373</v>
+        <v>-3.197672279208188</v>
       </c>
       <c r="G100">
-        <v>-8.428127027457572</v>
+        <v>-11.18011732334292</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.11822235752418</v>
       </c>
       <c r="E101">
-        <v>-46.50622103292213</v>
+        <v>-47.90196238495924</v>
       </c>
       <c r="F101">
-        <v>-3.306245566325716</v>
+        <v>-3.639713147996685</v>
       </c>
       <c r="G101">
-        <v>-9.573281145492407</v>
+        <v>-11.55070972264556</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.96307158100156</v>
       </c>
       <c r="E102">
-        <v>-48.67064480903574</v>
+        <v>-49.59486106926119</v>
       </c>
       <c r="F102">
-        <v>-3.574696247285757</v>
+        <v>-3.673081443716254</v>
       </c>
       <c r="G102">
-        <v>-9.56767970243996</v>
+        <v>-11.26808513941244</v>
       </c>
     </row>
   </sheetData>
